--- a/Result/profitability/3499.xlsx
+++ b/Result/profitability/3499.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.83</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3175</v>
+        <v>-0.335</v>
       </c>
       <c r="N2" t="n">
-        <v>21.65875</v>
+        <v>21.055</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.29</v>
+        <v>-0.365</v>
       </c>
       <c r="N3" t="n">
-        <v>20.465</v>
+        <v>19.83625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>-0.275</v>
       </c>
       <c r="N4" t="n">
-        <v>19.79125</v>
+        <v>19.99</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.21875</v>
+        <v>-0.19125</v>
       </c>
       <c r="N5" t="n">
-        <v>19.7</v>
+        <v>19.9625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1675</v>
+        <v>-0.1725</v>
       </c>
       <c r="N6" t="n">
-        <v>19.4275</v>
+        <v>19.22375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.16375</v>
+        <v>-0.18375</v>
       </c>
       <c r="N7" t="n">
-        <v>19.2075</v>
+        <v>19.03375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.14875</v>
+        <v>-0.125</v>
       </c>
       <c r="N8" t="n">
-        <v>18.76125</v>
+        <v>19.9625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.65</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.003749999999999976</v>
+        <v>-0.003749999999999962</v>
       </c>
       <c r="N9" t="n">
         <v>20.07625</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>86</v>
+      </c>
+      <c r="D75" t="n">
+        <v>67</v>
+      </c>
+      <c r="E75" t="n">
+        <v>19</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-20.59%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.25375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.4475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3725490196078431</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.7455391776570985</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4074074074074074</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.100000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1029411764705883</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
